--- a/information_request_forms/042_digital_wallet_issue_contact_form--information_request_forms.xlsx
+++ b/information_request_forms/042_digital_wallet_issue_contact_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'chat',_'label':_'live_chat'}</t>
+          <t>live_chat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'chat', 'label': 'Live Chat'}</t>
+          <t>Live Chat</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'windows',_'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'windows', 'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'ios',_'label':_'ios'}</t>
+          <t>ios</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'ios', 'label': 'iOS'}</t>
+          <t>iOS</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'android',_'label':_'android'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'android', 'label': 'Android'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'digital-wallets',_'label':_'digital_wallets'}</t>
+          <t>digital_wallets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'digital-wallets', 'label': 'Digital Wallets'}</t>
+          <t>Digital Wallets</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'account-management',_'label':_'account_management'}</t>
+          <t>account_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'account-management', 'label': 'Account Management'}</t>
+          <t>Account Management</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'transactions',_'label':_'transactions'}</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'transactions', 'label': 'Transactions'}</t>
+          <t>Transactions</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'live-chat',_'label':_'live_chat'}</t>
+          <t>live_chat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'live-chat', 'label': 'Live Chat'}</t>
+          <t>Live Chat</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'english', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'french',_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'french', 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'usa',_'label':_'united_states'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'usa', 'label': 'United States'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'canada',_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'canada', 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'mexico',_'label':_'mexico'}</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'mexico', 'label': 'Mexico'}</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
